--- a/exports/colleges/25703_iit-bombay-indian-institute-of-technology-iitb-mumbai.xlsx
+++ b/exports/colleges/25703_iit-bombay-indian-institute-of-technology-iitb-mumbai.xlsx
@@ -570,7 +570,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>CD Rank #6</t>
+          <t>Not Ranked</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -605,19 +605,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L81"/>
+  <dimension ref="A1:L99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="53" customWidth="1" min="3" max="3"/>
-    <col width="53" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="91" customWidth="1" min="3" max="3"/>
+    <col width="91" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="35" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
@@ -707,12 +707,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>8.33 Lakhs</t>
+          <t>8.33 L</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -722,17 +722,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pass in Graduation + GATE</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>GATE, COAP</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>25 Mar - 11 Apr 2026</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -769,12 +769,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>11.96 Lakhs</t>
+          <t>11.96 L</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>10+2 with 75% + JEE Advanced</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 June - 11 Jun 2026</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -831,12 +831,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2.66 Lakhs</t>
+          <t>2.66 L</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -846,17 +846,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Graduation + JAM</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>IIT JAM, JOAPS</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>27 Mar - 15 Apr 2026</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -888,17 +888,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>M.Phil/Ph.D in Arts</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.59 Lakhs</t>
+          <t>3.59 L</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Post Graduation</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>25 Mar - 11 Apr 2026</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BS</t>
+          <t>Bachelor of Science [BS]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -950,17 +950,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bachelor of Science [BS]</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11.96 Lakhs</t>
+          <t>11.96 L</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -970,17 +970,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>10+2 + JEE Advanced</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 June - 12 Jun 2025</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1002,27 +1002,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>M.Des</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>Master of Design [M.Des]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>Master of Design [M.Des]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6,000 - 5.48 Lakhs</t>
+          <t>3.05 L</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1037,12 +1037,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>CEED</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>9 Mar - 23 Mar 2026</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1064,27 +1064,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>B.Des</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>Bachelor of Design [B.Des]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>Bachelor of Design [B.Des]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11.96 Lakhs - 14.87 Lakhs</t>
+          <t>11.96 L</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>UCEED</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>14 Mar - 03 Apr 2026</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1126,27 +1126,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>Master of Business Administration [MBA]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>Master of Business Administration [MBA]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.24 Lakhs - 7.85 Lakhs</t>
+          <t>17.3 L</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 Jan - 31 Jan 2026</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1188,27 +1188,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>Master of Science [M.S]</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>Master of Science [M.S]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.2 Lakhs - 3.97 Lakhs</t>
+          <t>3.05 L</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>27 Mar - 15 Apr 2026</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1250,27 +1250,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BS</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BS</t>
+          <t>Bachelor of Technology [B.Tech] + Master of Technology [M.Tech] (Electrical Engineering)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>BS</t>
+          <t>Bachelor of Technology [B.Tech] + Master of Technology [M.Tech] (Electrical Engineering)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>17.57 Lakhs</t>
+          <t>14.87 L</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1285,12 +1285,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 June - 11 Jun 2026</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1312,27 +1312,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>M.Des</t>
+          <t>MPP</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>M.Des</t>
+          <t>Master of Public Policy [MPP]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>M.Des</t>
+          <t>Master of Public Policy [MPP]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2.41 Lakhs</t>
+          <t>3.05 L</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CEED</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>25 Mar - 11 Apr 2026</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1374,27 +1374,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>B.Des</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B.Des</t>
+          <t>Master of Technology [M.Tech] + Ph.D</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>B.Des</t>
+          <t>Master of Technology [M.Tech] + Ph.D</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>17.57 Lakhs</t>
+          <t>7.15 L</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1409,12 +1409,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>UCEED</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>25 Mar - 11 Apr 2026</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1436,27 +1436,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>Master of Science [M.Sc] + Ph.D</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>Master of Science [M.Sc] + Ph.D</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>23.64 Lakhs</t>
+          <t>7.35 L</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1471,12 +1471,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>27 Mar - 15 Apr 2026</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1498,32 +1498,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>EMBA</t>
+          <t>Master of Arts [MA] + Ph.D. (Philosophy)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>EMBA</t>
+          <t>Master of Arts [MA] + Ph.D. (Philosophy)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>45 Lakhs</t>
+          <t>7.35 L</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Part Time</t>
+          <t>Full Time</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1533,12 +1533,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>25 Mar - 11 Apr 2026</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1560,27 +1560,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Computer Science And Engineering</t>
+          <t>Bachelor of Technology [B.Tech] (Industrial Engineering and Operations Research)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Computer Science And Engineering</t>
+          <t>Bachelor of Technology [B.Tech] (Industrial Engineering and Operations Research)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2.41 Lakhs</t>
+          <t>11.96 L</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 June - 11 Jun 2026</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1622,27 +1622,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>Bachelor of Science [BS] (Applied Geophysics)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Biomedical Engineering</t>
+          <t>Bachelor of Science [BS] (Applied Geophysics)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Biomedical Engineering</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2.41 Lakhs</t>
+          <t>11.96 L</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 June - 12 Jun 2025</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1689,27 +1689,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Integrated Circuit Technology</t>
+          <t>Master of Technology [M.Tech]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Integrated Circuit Technology</t>
+          <t>Master of Technology [M.Tech]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2.41 Lakhs</t>
+          <t>4.41 L</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>25 Mar - 11 Apr 2026</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1746,32 +1746,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chemical Engineering</t>
+          <t>Executive Post Graduate Diploma in Management [Ex-PGDM]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Chemical Engineering</t>
+          <t>Executive Post Graduate Diploma in Management [Ex-PGDM]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2.41 Lakhs</t>
+          <t>3 L - 6 L</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>1 year 6 months</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1781,12 +1781,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>13 Mar 2025</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1813,17 +1813,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Geoinformatics &amp; Natural Resources Engineering</t>
+          <t>Master of Technology [M.Tech]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Geoinformatics &amp; Natural Resources Engineering</t>
+          <t>Master of Technology [M.Tech]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2.41 Lakhs</t>
+          <t>8.33 Lakhs</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Pass in Graduation + GATE</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>GATE, COAP</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1870,27 +1870,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Educational Technology</t>
+          <t>Bachelor of Technology [B.Tech]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Educational Technology</t>
+          <t>Bachelor of Technology [B.Tech]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2.41 Lakhs</t>
+          <t>11.96 Lakhs</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10+2 with 75% + JEE Advanced</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1932,22 +1932,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Structural Engineering</t>
+          <t>Master of Science [M.Sc]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Structural Engineering</t>
+          <t>Master of Science [M.Sc]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2.41 Lakhs</t>
+          <t>2.66 Lakhs</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1962,12 +1962,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation + JAM</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>IIT JAM, JOAPS</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1994,27 +1994,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Environmental Science And Engineering</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Environmental Science And Engineering</t>
+          <t>M.Phil/Ph.D in Arts</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2.41 Lakhs</t>
+          <t>3.59 Lakhs</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>3 Years</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2024,12 +2024,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Post Graduation</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -2056,27 +2056,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>BS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Material Science And Engineering</t>
+          <t>Bachelor of Science [BS]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Material Science And Engineering</t>
+          <t>Bachelor of Science [BS]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2.41 Lakhs</t>
+          <t>11.96 Lakhs</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2086,12 +2086,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10+2 + JEE Advanced</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -2123,17 +2123,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Construction Management</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Construction Management</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2.41 Lakhs</t>
+          <t>6,000 - 5.48 Lakhs</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2180,27 +2180,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Power Systems And Power Electronics</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Power Systems And Power Electronics</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2.41 Lakhs</t>
+          <t>11.96 Lakhs - 14.87 Lakhs</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -2242,22 +2242,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Design Engineering</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Design Engineering</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2.41 Lakhs</t>
+          <t>1.24 Lakhs - 7.85 Lakhs</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2304,27 +2304,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Systems &amp; Control Engineering</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Systems &amp; Control Engineering</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2.41 Lakhs</t>
+          <t>2.2 Lakhs - 3.97 Lakhs</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>3-5 Years</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -2366,27 +2366,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>BS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Communication Engineering</t>
+          <t>BS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Communication Engineering</t>
+          <t>BS</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2.41 Lakhs</t>
+          <t>17.57 Lakhs</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -2428,17 +2428,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>M.Des</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Aerospace Structure</t>
+          <t>M.Des</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Aerospace Structure</t>
+          <t>M.Des</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>CEED</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2490,27 +2490,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>B.Des</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Electronic Systems</t>
+          <t>B.Des</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Electronic Systems</t>
+          <t>B.Des</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2.41 Lakhs</t>
+          <t>17.57 Lakhs</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>UCEED</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -2552,22 +2552,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Corrosion Science &amp; Technology</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Corrosion Science &amp; Technology</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2.41 Lakhs</t>
+          <t>23.64 Lakhs</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2614,22 +2614,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>M.Tech</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Petroleum Geoscience</t>
+          <t>EMBA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Petroleum Geoscience</t>
+          <t>EMBA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2.41 Lakhs</t>
+          <t>45 Lakhs</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>GATE</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote Sensing</t>
+          <t>Computer Science And Engineering</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Remote Sensing</t>
+          <t>Computer Science And Engineering</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2743,12 +2743,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Semiconductor Materials and Processing</t>
+          <t>Biomedical Engineering</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Semiconductor Materials and Processing</t>
+          <t>Biomedical Engineering</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Thermal - Fluid</t>
+          <t>Integrated Circuit Technology</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Thermal - Fluid</t>
+          <t>Integrated Circuit Technology</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Geoexploration</t>
+          <t>Chemical Engineering</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Geoexploration</t>
+          <t>Chemical Engineering</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2929,12 +2929,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Steel Technology</t>
+          <t>Geoinformatics &amp; Natural Resources Engineering</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Steel Technology</t>
+          <t>Geoinformatics &amp; Natural Resources Engineering</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Geotechnical Engineering</t>
+          <t>Educational Technology</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Geotechnical Engineering</t>
+          <t>Educational Technology</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Transportation Engineering</t>
+          <t>Structural Engineering</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Transportation Engineering</t>
+          <t>Structural Engineering</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3115,12 +3115,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Control &amp; Computing</t>
+          <t>Environmental Science And Engineering</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Control &amp; Computing</t>
+          <t>Environmental Science And Engineering</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Materials, Manufacturing and Modeling</t>
+          <t>Material Science And Engineering</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Materials, Manufacturing and Modeling</t>
+          <t>Material Science And Engineering</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3239,12 +3239,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ocean Engineering</t>
+          <t>Construction Management</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Ocean Engineering</t>
+          <t>Construction Management</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Technology and Development</t>
+          <t>Power Systems And Power Electronics</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Technology and Development</t>
+          <t>Power Systems And Power Electronics</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Aerospace Propulsion</t>
+          <t>Design Engineering</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Aerospace Propulsion</t>
+          <t>Design Engineering</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3425,12 +3425,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Energy System Engineering</t>
+          <t>Systems &amp; Control Engineering</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Energy System Engineering</t>
+          <t>Systems &amp; Control Engineering</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3487,12 +3487,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dynamics &amp; Control</t>
+          <t>Communication Engineering</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Dynamics &amp; Control</t>
+          <t>Communication Engineering</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Solid State Materials</t>
+          <t>Aerospace Structure</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Solid State Materials</t>
+          <t>Aerospace Structure</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3611,12 +3611,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Computational Materials Engineering</t>
+          <t>Electronic Systems</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Computational Materials Engineering</t>
+          <t>Electronic Systems</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Aerodynamics</t>
+          <t>Corrosion Science &amp; Technology</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Aerodynamics</t>
+          <t>Corrosion Science &amp; Technology</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Climate and  Sustainability</t>
+          <t>Petroleum Geoscience</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Climate and  Sustainability</t>
+          <t>Petroleum Geoscience</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Water Resources Engineering</t>
+          <t>Remote Sensing</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Water Resources Engineering</t>
+          <t>Remote Sensing</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3859,17 +3859,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Manufacturing Processes and Automation Engineering</t>
+          <t>Semiconductor Materials and Processing</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Manufacturing Processes and Automation Engineering</t>
+          <t>Semiconductor Materials and Processing</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.24 Lakhs</t>
+          <t>2.41 Lakhs</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3916,27 +3916,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Computer Science and Engineering</t>
+          <t>Thermal - Fluid</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Computer Science and Engineering</t>
+          <t>Thermal - Fluid</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>11.96 Lakhs</t>
+          <t>2.41 Lakhs</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -3978,27 +3978,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Aerospace Engineering</t>
+          <t>Geoexploration</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Aerospace Engineering</t>
+          <t>Geoexploration</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>11.96 Lakhs</t>
+          <t>2.41 Lakhs</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -4040,27 +4040,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Mechanical Engineering</t>
+          <t>Steel Technology</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Mechanical Engineering</t>
+          <t>Steel Technology</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>11.96 Lakhs</t>
+          <t>2.41 Lakhs</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -4102,27 +4102,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Geotechnical Engineering</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Geotechnical Engineering</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>11.96 Lakhs</t>
+          <t>2.41 Lakhs</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -4164,27 +4164,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chemical Engineering</t>
+          <t>Transportation Engineering</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Chemical Engineering</t>
+          <t>Transportation Engineering</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>11.96 Lakhs</t>
+          <t>2.41 Lakhs</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -4226,27 +4226,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Metallurgical And Materials Engineering</t>
+          <t>Control &amp; Computing</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Metallurgical And Materials Engineering</t>
+          <t>Control &amp; Computing</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>11.96 Lakhs</t>
+          <t>2.41 Lakhs</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -4288,27 +4288,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Engineering Physics</t>
+          <t>Materials, Manufacturing and Modeling</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Engineering Physics</t>
+          <t>Materials, Manufacturing and Modeling</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>11.96 Lakhs</t>
+          <t>2.41 Lakhs</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4323,7 +4323,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -4350,27 +4350,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Environmental Engineering</t>
+          <t>Ocean Engineering</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Environmental Engineering</t>
+          <t>Ocean Engineering</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>11.96 Lakhs</t>
+          <t>2.41 Lakhs</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -4412,27 +4412,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>B.Tech</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Energy Engineering</t>
+          <t>Technology and Development</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Energy Engineering</t>
+          <t>Technology and Development</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>11.96 Lakhs</t>
+          <t>2.41 Lakhs</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>JEE Advanced</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -4474,22 +4474,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Aerospace Propulsion</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Aerospace Propulsion</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2.48 Lakhs</t>
+          <t>2.41 Lakhs</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4536,22 +4536,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Energy System Engineering</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Energy System Engineering</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2.48 Lakhs</t>
+          <t>2.41 Lakhs</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4598,22 +4598,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Dynamics &amp; Control</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Dynamics &amp; Control</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2.48 Lakhs</t>
+          <t>2.41 Lakhs</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4660,22 +4660,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chemistry</t>
+          <t>Solid State Materials</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Chemistry</t>
+          <t>Solid State Materials</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2.48 Lakhs</t>
+          <t>2.41 Lakhs</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4722,22 +4722,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Applied Geology</t>
+          <t>Computational Materials Engineering</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Applied Geology</t>
+          <t>Computational Materials Engineering</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2.48 Lakhs</t>
+          <t>2.41 Lakhs</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4784,22 +4784,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Statistics</t>
+          <t>Aerodynamics</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Statistics</t>
+          <t>Aerodynamics</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2.48 Lakhs</t>
+          <t>2.41 Lakhs</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4846,22 +4846,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Operations Research</t>
+          <t>Climate and  Sustainability</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Operations Research</t>
+          <t>Climate and  Sustainability</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2.48 Lakhs</t>
+          <t>2.41 Lakhs</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4908,27 +4908,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ph.D (General)</t>
+          <t>Water Resources Engineering</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Water Resources Engineering</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2.2 Lakhs - 3.97 Lakhs</t>
+          <t>2.41 Lakhs</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -4970,27 +4970,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>M.Tech</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Manufacturing Processes and Automation Engineering</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Manufacturing Processes and Automation Engineering</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>3.4 Lakhs</t>
+          <t>1.24 Lakhs</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5000,12 +5000,12 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Postgraduation in relevant field</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>GATE</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -5032,27 +5032,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Computer Science and Engineering</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Computer Science and Engineering</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>3.4 Lakhs</t>
+          <t>11.96 Lakhs</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5062,12 +5062,12 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Postgraduation in relevant field</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -5094,27 +5094,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Humanities And Social Science</t>
+          <t>Aerospace Engineering</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Humanities And Social Science</t>
+          <t>Aerospace Engineering</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>3.4 Lakhs</t>
+          <t>11.96 Lakhs</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Postgraduation in relevant field</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -5156,27 +5156,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Public Policy</t>
+          <t>Mechanical Engineering</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Public Policy</t>
+          <t>Mechanical Engineering</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>3.4 Lakhs</t>
+          <t>11.96 Lakhs</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5186,12 +5186,12 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Postgraduation in relevant field</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -5218,25 +5218,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BS</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>BS (General)</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>17.57 Lakhs</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr"/>
+          <t>11.96 Lakhs</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>4 Years</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr">
         <is>
           <t>Full Time</t>
@@ -5249,7 +5253,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5276,27 +5280,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>M.Des</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>M.Des (General)</t>
+          <t>Chemical Engineering</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Chemical Engineering</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2.41 Lakhs</t>
+          <t>11.96 Lakhs</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5311,7 +5315,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>CEED</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5326,7 +5330,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -5338,22 +5342,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>B.Des</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>B.Des (General)</t>
+          <t>Metallurgical And Materials Engineering</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Metallurgical And Materials Engineering</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>17.57 Lakhs</t>
+          <t>11.96 Lakhs</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -5373,7 +5377,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>UCEED</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5400,27 +5404,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MBA (General)</t>
+          <t>Engineering Physics</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Engineering Physics</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>23.64 Lakhs</t>
+          <t>11.96 Lakhs</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5435,7 +5439,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5450,7 +5454,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -5462,27 +5466,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Environmental Engineering</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Environmental Engineering</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>23.64 Lakhs</t>
+          <t>11.96 Lakhs</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5492,12 +5496,12 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Graduation with 60%+</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5512,7 +5516,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -5524,27 +5528,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>B.Tech</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Telecommunication Systems Management</t>
+          <t>Energy Engineering</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Telecommunication Systems Management</t>
+          <t>Energy Engineering</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>23.64 Lakhs</t>
+          <t>11.96 Lakhs</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5554,12 +5558,12 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Graduation with 60%+</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>JEE Advanced</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5574,7 +5578,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -5586,55 +5590,1167 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
+          <t>M.Sc</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Biotechnology</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Biotechnology</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2.48 Lakhs</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>IIT JAM</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>25703</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>M.Sc</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2.48 Lakhs</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>IIT JAM</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>25703</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>M.Sc</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2.48 Lakhs</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>IIT JAM</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>25703</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>M.Sc</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2.48 Lakhs</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>IIT JAM</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>25703</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>M.Sc</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Applied Geology</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Applied Geology</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2.48 Lakhs</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>IIT JAM</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>25703</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>M.Sc</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Statistics</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Statistics</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2.48 Lakhs</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>IIT JAM</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>25703</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>M.Sc</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Operations Research</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Operations Research</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2.48 Lakhs</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>IIT JAM</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>25703</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Ph.D</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Ph.D (General)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>2.2 Lakhs - 3.97 Lakhs</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>3-5 Years</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>GATE / UGC NET</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Doctorate</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>25703</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Ph.D</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>3.4 Lakhs</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>3-5 Years</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Postgraduation in relevant field</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>GATE / UGC NET</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Doctorate</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>25703</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Ph.D</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>3.4 Lakhs</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>3-5 Years</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Postgraduation in relevant field</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>GATE / UGC NET</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Doctorate</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>25703</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Ph.D</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Humanities And Social Science</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Humanities And Social Science</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>3.4 Lakhs</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>3-5 Years</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Postgraduation in relevant field</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>GATE / UGC NET</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Doctorate</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>25703</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Ph.D</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Public Policy</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Public Policy</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>3.4 Lakhs</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>3-5 Years</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Postgraduation in relevant field</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>GATE / UGC NET</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Doctorate</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>25703</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>BS (General)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>17.57 Lakhs</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>25703</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>M.Des</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>M.Des (General)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>2.41 Lakhs</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>CEED</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>25703</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>B.Des</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>B.Des (General)</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>17.57 Lakhs</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>4 Years</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>UCEED</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>25703</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>MBA (General)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>23.64 Lakhs</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>25703</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>23.64 Lakhs</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Graduation with 60%+</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>25703</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Telecommunication Systems Management</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Telecommunication Systems Management</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>23.64 Lakhs</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Graduation with 60%+</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>25703</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
           <t>EMBA</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>EMBA (General)</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="E99" t="inlineStr">
         <is>
           <t>45 Lakhs</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F99" t="inlineStr">
         <is>
           <t>2 Years</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t>Part Time</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
         <is>
           <t>CAT</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
         <is>
           <t>PG</t>
         </is>
@@ -5788,12 +6904,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1,00,00,000</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>23,50,000</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -5803,7 +6919,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -5823,13 +6939,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5840,17 +6954,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>ranking_body</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>rank</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>ranking_year</t>
+          <t>status</t>
         </is>
       </c>
     </row>
@@ -5862,15 +6966,9 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Collegedunia</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>CD Rank #6</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>No Data Available</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
